--- a/outputs/evaluation/architecture/validation/gemini-3-5/CF_M09/run_3/CF_M09_arch_eval.xlsx
+++ b/outputs/evaluation/architecture/validation/gemini-3-5/CF_M09/run_3/CF_M09_arch_eval.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -440,6 +440,11 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>f1</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>mean semantic meaning</t>
         </is>
       </c>
@@ -456,7 +461,10 @@
       <c r="C2" t="n">
         <v>0.6875</v>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" t="n">
+        <v>0.7416</v>
+      </c>
+      <c r="E2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -475,6 +483,9 @@
         <v>0.7442</v>
       </c>
       <c r="D3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E3" t="n">
         <v>0.9699</v>
       </c>
     </row>
@@ -491,6 +502,9 @@
         <v>0.2</v>
       </c>
       <c r="D4" t="n">
+        <v>0.2222</v>
+      </c>
+      <c r="E4" t="n">
         <v>0.7589</v>
       </c>
     </row>
@@ -1201,7 +1215,6 @@
       <c r="D2" t="n">
         <v>0.7589</v>
       </c>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1222,7 +1235,6 @@
           <t>['AU_10', 'AU_11']</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
           <t>AU_32</t>
@@ -1233,7 +1245,6 @@
           <t>business service, functional service</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1252,7 +1263,6 @@
           <t>CF_M09_AU06, CF_M09_AU19</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
           <t>CF_M09_AU20</t>
@@ -1308,13 +1318,11 @@
           <t>['AU_04']</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
           <t>AU_10</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
           <t>Business layer</t>
@@ -1338,13 +1346,11 @@
           <t>CF_M09_P02</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
         <is>
           <t>CF_M09_AU09</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1390,13 +1396,11 @@
           <t>['P_03']</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
           <t>P_04</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
           <t>Observer pattern</t>
@@ -1420,13 +1424,11 @@
           <t>CF_M09_P03</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
           <t>CF_M09_P04</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1472,13 +1474,11 @@
           <t>['AU_31']</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
           <t>AU_19</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
           <t>REST</t>
@@ -1502,13 +1502,11 @@
           <t>CF_M09_AU20</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
         <is>
           <t>CF_M09_AU22</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1549,14 +1547,11 @@
           <t>59</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
           <t>P_05</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
           <t>Provider pattern</t>
@@ -1580,13 +1575,11 @@
           <t>CF_M09_AU01</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr">
         <is>
           <t>CF_M09_P05</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1627,14 +1620,11 @@
           <t>59</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
           <t>P_07</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
           <t>Hook pattern</t>
@@ -1658,13 +1648,11 @@
           <t>CF_M09_AU01</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
         <is>
           <t>CF_M09_P07</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1705,14 +1693,11 @@
           <t>55</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
           <t>P_01</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
           <t>Client-Server Architecture</t>
@@ -1731,14 +1716,11 @@
       <c r="P8" t="n">
         <v>55</v>
       </c>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr">
         <is>
           <t>CF_M09_P01</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1784,13 +1766,11 @@
           <t>['P_02']</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
           <t>AU_04</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
           <t>Business layer (Backend)</t>
@@ -1814,13 +1794,11 @@
           <t>CF_M09_P02</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr">
         <is>
           <t>CF_M09_AU19</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1866,13 +1844,11 @@
           <t>['P_02']</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
           <t>AU_03</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
           <t>Presentation layer</t>
@@ -1896,13 +1872,11 @@
           <t>CF_M09_P02</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr">
         <is>
           <t>CF_M09_AU08</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1948,13 +1922,11 @@
           <t>['P_02']</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
           <t>AU_05</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
           <t>Data layer</t>
@@ -1978,13 +1950,11 @@
           <t>CF_M09_P02</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr">
         <is>
           <t>CF_M09_AU10</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2025,14 +1995,11 @@
           <t>60</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
           <t>AU_23</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
           <t>Typescript</t>
@@ -2056,13 +2023,11 @@
           <t>CF_M09_AU26</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr">
         <is>
           <t>CF_M09_AU28</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2108,13 +2073,11 @@
           <t>['AU_03']</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
           <t>AU_17</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
           <t>React</t>
@@ -2138,13 +2101,11 @@
           <t>CF_M09_AU34</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr">
         <is>
           <t>CF_M09_AU01</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2190,13 +2151,11 @@
           <t>['AU_17']</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
           <t>AU_25</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
           <t>Material UI</t>
@@ -2220,13 +2179,11 @@
           <t>CF_M09_AU01</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr">
         <is>
           <t>CF_M09_AU30</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2272,13 +2229,11 @@
           <t>['AU_12', 'AU_34']</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
           <t>AU_13</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
           <t>MySQL</t>
@@ -2302,13 +2257,11 @@
           <t>CF_M09_AU23</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr">
         <is>
           <t>CF_M09_AU24</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2354,13 +2307,11 @@
           <t>['P_03']</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
           <t>AU_08</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
           <t>Dispatcher</t>
@@ -2384,13 +2335,11 @@
           <t>CF_M09_P03</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr">
         <is>
           <t>CF_M09_AU13</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2436,13 +2385,11 @@
           <t>['P_03']</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
           <t>AU_06</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
           <t>View</t>
@@ -2466,13 +2413,11 @@
           <t>CF_M09_P03</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr">
         <is>
           <t>CF_M09_AU11</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2518,13 +2463,11 @@
           <t>['AU_31']</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
           <t>AU_20</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
           <t>HTTP</t>
@@ -2543,14 +2486,11 @@
       <c r="P18" t="n">
         <v>55</v>
       </c>
-      <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr">
         <is>
           <t>CF_M09_AU40</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2591,14 +2531,11 @@
           <t>61</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
           <t>AU_28</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
           <t>Shadcn</t>
@@ -2622,13 +2559,11 @@
           <t>CF_M09_AU34</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr">
         <is>
           <t>CF_M09_AU32</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2674,13 +2609,11 @@
           <t>['P_03']</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
           <t>AU_07</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
           <t>Actions</t>
@@ -2704,13 +2637,11 @@
           <t>CF_M09_P03</t>
         </is>
       </c>
-      <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr">
         <is>
           <t>CF_M09_AU12</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2756,13 +2687,11 @@
           <t>['P_03']</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
           <t>AU_09</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
           <t>Store</t>
@@ -2786,13 +2715,11 @@
           <t>CF_M09_P03</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr">
         <is>
           <t>CF_M09_AU14</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2838,13 +2765,11 @@
           <t>['AU_04']</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
           <t>AU_22</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
           <t>NestJS</t>
@@ -2868,13 +2793,11 @@
           <t>CF_M09_AU33</t>
         </is>
       </c>
-      <c r="R22" t="inlineStr"/>
       <c r="S22" t="inlineStr">
         <is>
           <t>CF_M09_AU02</t>
         </is>
       </c>
-      <c r="T22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2915,14 +2838,11 @@
           <t>60</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
           <t>AU_24</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
           <t>TypeORM</t>
@@ -2946,13 +2866,11 @@
           <t>CF_M09_AU33</t>
         </is>
       </c>
-      <c r="R23" t="inlineStr"/>
       <c r="S23" t="inlineStr">
         <is>
           <t>CF_M09_AU29</t>
         </is>
       </c>
-      <c r="T23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2998,13 +2916,11 @@
           <t>['P_01']</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
           <t>AU_01</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
           <t>Client</t>
@@ -3028,13 +2944,11 @@
           <t>CF_M09_P01</t>
         </is>
       </c>
-      <c r="R24" t="inlineStr"/>
       <c r="S24" t="inlineStr">
         <is>
           <t>CF_M09_AU06</t>
         </is>
       </c>
-      <c r="T24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3080,13 +2994,11 @@
           <t>['AU_05']</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
           <t>AU_14</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
           <t>Amazon S3</t>
@@ -3110,13 +3022,11 @@
           <t>CF_M09_AU39</t>
         </is>
       </c>
-      <c r="R25" t="inlineStr"/>
       <c r="S25" t="inlineStr">
         <is>
           <t>CF_M09_AU25</t>
         </is>
       </c>
-      <c r="T25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3162,13 +3072,11 @@
           <t>['AU_03']</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
           <t>AU_18</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
           <t>Redux</t>
@@ -3192,13 +3100,11 @@
           <t>CF_M09_P03</t>
         </is>
       </c>
-      <c r="R26" t="inlineStr"/>
       <c r="S26" t="inlineStr">
         <is>
           <t>CF_M09_AU17</t>
         </is>
       </c>
-      <c r="T26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3239,14 +3145,11 @@
           <t>61</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
           <t>AU_27</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
           <t>NextJS</t>
@@ -3270,13 +3173,11 @@
           <t>CF_M09_AU01</t>
         </is>
       </c>
-      <c r="R27" t="inlineStr"/>
       <c r="S27" t="inlineStr">
         <is>
           <t>CF_M09_AU31</t>
         </is>
       </c>
-      <c r="T27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3322,13 +3223,11 @@
           <t>['P_02']</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
         <is>
           <t>P_03</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
           <t>Flux</t>
@@ -3352,13 +3251,11 @@
           <t>CF_M09_AU34</t>
         </is>
       </c>
-      <c r="R28" t="inlineStr"/>
       <c r="S28" t="inlineStr">
         <is>
           <t>CF_M09_P03</t>
         </is>
       </c>
-      <c r="T28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3399,14 +3296,11 @@
           <t>61</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
           <t>AU_26</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
           <t>AWS</t>
@@ -3425,14 +3319,11 @@
       <c r="P29" t="n">
         <v>9</v>
       </c>
-      <c r="Q29" t="inlineStr"/>
-      <c r="R29" t="inlineStr"/>
       <c r="S29" t="inlineStr">
         <is>
           <t>CF_M09_AU03</t>
         </is>
       </c>
-      <c r="T29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -3478,13 +3369,11 @@
           <t>['P_01']</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
           <t>P_02</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
           <t>Three Layers</t>
@@ -3503,14 +3392,11 @@
       <c r="P30" t="n">
         <v>55</v>
       </c>
-      <c r="Q30" t="inlineStr"/>
-      <c r="R30" t="inlineStr"/>
       <c r="S30" t="inlineStr">
         <is>
           <t>CF_M09_P02</t>
         </is>
       </c>
-      <c r="T30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3556,13 +3442,11 @@
           <t>['AU_15']</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
           <t>AU_16</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
           <t>Amazon DynamoDB</t>
@@ -3586,13 +3470,11 @@
           <t>CF_M09_AU10</t>
         </is>
       </c>
-      <c r="R31" t="inlineStr"/>
       <c r="S31" t="inlineStr">
         <is>
           <t>CF_M09_AU27</t>
         </is>
       </c>
-      <c r="T31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -3638,13 +3520,11 @@
           <t>['AU_05']</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
         <is>
           <t>AU_12</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
           <t>RDS</t>
@@ -3668,13 +3548,11 @@
           <t>CF_M09_AU39</t>
         </is>
       </c>
-      <c r="R32" t="inlineStr"/>
       <c r="S32" t="inlineStr">
         <is>
           <t>CF_M09_AU23</t>
         </is>
       </c>
-      <c r="T32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -3720,13 +3598,11 @@
           <t>['AU_05']</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
           <t>AU_15</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
           <t>User Cache</t>
@@ -3750,13 +3626,11 @@
           <t>CF_M09_AU39</t>
         </is>
       </c>
-      <c r="R33" t="inlineStr"/>
       <c r="S33" t="inlineStr">
         <is>
           <t>CF_M09_AU26</t>
         </is>
       </c>
-      <c r="T33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -3802,13 +3676,11 @@
           <t>['AU_32']</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
           <t>AU_21</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
           <t>TCP</t>
@@ -3832,13 +3704,11 @@
           <t>CF_M09_AU20</t>
         </is>
       </c>
-      <c r="R34" t="inlineStr"/>
       <c r="S34" t="inlineStr">
         <is>
           <t>CF_M09_AU21</t>
         </is>
       </c>
-      <c r="T34" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3912,7 +3782,6 @@
           <t>Server</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>Por un lado está el cliente, quien realiza las diferentes peticiones, y por otro lado está el servidor, quien las recibe y las procesa.</t>
@@ -3948,7 +3817,6 @@
           <t>Functional Service</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>Servicio functional: Este es el servicio que realiza toda la lógica importante de la plataforma.</t>
@@ -3984,7 +3852,6 @@
           <t>NodeJS</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>NestJS: [3] es un framework de NodeJS para crear aplicaciones backend.</t>
@@ -4020,7 +3887,6 @@
           <t>JavaScript</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>TypeScript: [39] es un superconjunto de JavaScript.</t>
@@ -4051,7 +3917,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
           <t>client, server</t>
@@ -4087,7 +3952,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
           <t>business service, amazon dynamodb</t>
@@ -4123,7 +3987,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
           <t>functional service, mysql</t>
@@ -4164,7 +4027,6 @@
           <t>Module</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
           <t>Este es el patrón más importante dentro del lenguaje de JavaScript. Este patrón permite encapsular la información y exponer solo aquella que se desea compartir entre módulos (como funciones o componentes).</t>
@@ -4256,7 +4118,6 @@
           <t>Player</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>A player is an external device that allows content to be played on a non professional screen.</t>
@@ -4292,7 +4153,6 @@
           <t>Waapiti Platform</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>The main objective of this work is the development of an asset management module that expands the Waapiti software platform and allows us to solve a series of problems and needs of the company.</t>
@@ -4303,7 +4163,6 @@
           <t>AU_34</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
         <v>0.6631</v>
       </c>
@@ -4319,7 +4178,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
           <t>client, waapiti platform</t>
@@ -4355,7 +4213,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
           <t>actions, store</t>
@@ -4391,7 +4248,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
           <t>dispatcher, store</t>
@@ -4432,7 +4288,6 @@
           <t>Presentation layer (Backend)</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
           <t>In this case, the presentation layer is not complex. It corresponds to the user's web browser.</t>
@@ -4468,7 +4323,6 @@
           <t>Backend</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>It should be clear that in this project the author has worked on the entire system, both backend and frontend.</t>
@@ -4504,7 +4358,6 @@
           <t>Frontend</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
           <t>It should be clear that in this project the author has worked on the entire system, both backend and frontend.</t>
@@ -4540,7 +4393,6 @@
           <t>Modules</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>Modules are classes that allow NestJS to organize the application.</t>
@@ -4576,7 +4428,6 @@
           <t>Controllers</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>Controllers are responsible for receiving and processing HTTP requests.</t>
@@ -4612,7 +4463,6 @@
           <t>Providers</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
           <t>Providers are classes that can act as services, repositories, factories, helpers, etc.</t>
@@ -4643,7 +4493,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
           <t>client, business layer (backend)</t>
@@ -4684,7 +4533,6 @@
           <t>Data Layer (Backend)</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>The data layer is divided into several AWS services that allow for improved system performance and scalability.</t>
@@ -4720,7 +4568,6 @@
           <t>Module Pattern</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>This is the most important pattern in the JavaScript language.</t>
@@ -4756,7 +4603,6 @@
           <t>ORM</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
           <t>TypeORM is an ORM (Object Relational Mapping) that allows you to define database entities as TypeScript classes.</t>
